--- a/course_data_2026/Phylogenetics/gtdb_phylogenetic_tree/Bednarski_2025_qcmags_hqMAGs_report.xlsx
+++ b/course_data_2026/Phylogenetics/gtdb_phylogenetic_tree/Bednarski_2025_qcmags_hqMAGs_report.xlsx
@@ -49,13 +49,13 @@
     <t>gtdbtk_closest_genome_reference</t>
   </si>
   <si>
-    <t>gunc_postqc_n_contigs</t>
+    <t>gunc_postqc_n_contigs.fa</t>
   </si>
   <si>
     <t>gunc_postqc_pass.GUNC</t>
   </si>
   <si>
-    <t>gunc_preqc_n_contigs</t>
+    <t>gunc_preqc_n_contigs.fa</t>
   </si>
   <si>
     <t>gunc_preqc_pass.GUNC</t>
@@ -4444,7 +4444,7 @@
     <t>SRR30598618_clean_bin.10.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.10.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.10.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618</t>
@@ -4459,7 +4459,7 @@
     <t>SRR30598618_clean_bin.11.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.11.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.11.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Christensenellales;f__Aristaeellaceae;g__Firm-10;s__Firm-10 sp934631025</t>
@@ -4471,19 +4471,19 @@
     <t>SRR30598618_clean_bin.13.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.13.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.13.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.16.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.16.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.16.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.18.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.18.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.18.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__Ruminiclostridium_E;s__Ruminiclostridium_E siraeum</t>
@@ -4495,19 +4495,19 @@
     <t>SRR30598618_clean_bin.2.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.2.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.2.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.22.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.22.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.22.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.27.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.27.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.27.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Negativicutes;o__Acidaminococcales;f__Acidaminococcaceae;g__Phascolarctobacterium_A;s__</t>
@@ -4516,19 +4516,19 @@
     <t>SRR30598618_clean_bin.28.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.28.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.28.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.29.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.29.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.29.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.3.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.3.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.3.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__Ruminococcus;s__Ruminococcus sp002438605</t>
@@ -4540,19 +4540,19 @@
     <t>SRR30598618_clean_bin.30.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.30.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.30.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.31.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.31.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.31.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.32.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.32.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.32.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Christensenellales;f__Aristaeellaceae;g__Ventricola;s__Ventricola sp900542395</t>
@@ -4564,7 +4564,7 @@
     <t>SRR30598618_clean_bin.33.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.33.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.33.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Peptostreptococcales;f__Anaerovoracaceae;g__UMGS973;s__UMGS973 sp900547295</t>
@@ -4576,7 +4576,7 @@
     <t>SRR30598618_clean_bin.37.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.37.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.37.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Peptostreptococcales;f__Anaerovoracaceae;g__Lentihominibacter;s__Lentihominibacter sp905193765</t>
@@ -4588,37 +4588,37 @@
     <t>SRR30598618_clean_bin.39.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.39.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.39.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.41.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.41.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.41.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.5.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.5.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.5.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.51.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.51.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.51.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.52.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.52.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.52.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.53.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.53.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.53.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Christensenellales;f__Aristaeellaceae;g__Faecivicinus;s__Faecivicinus sp900759005</t>
@@ -4630,7 +4630,7 @@
     <t>SRR30598618_clean_bin.54.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.54.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.54.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Flavobacteriales;f__UBA1820;g__Merdimorpha;s__Merdimorpha sp003150615</t>
@@ -4642,31 +4642,31 @@
     <t>SRR30598618_clean_bin.59.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.59.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.59.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.64.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.64.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.64.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.68.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.68.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.68.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.7.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.7.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.7.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.77.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.77.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.77.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Actinomycetota;c__Coriobacteriia;o__Coriobacteriales;f__Eggerthellaceae;g__Anaerotardibacter;s__Anaerotardibacter sp000435475</t>
@@ -4678,19 +4678,19 @@
     <t>SRR30598618_clean_bin.79.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.79.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.79.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.8.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.8.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.8.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.81.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.81.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.81.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Oscillospiraceae;g__HGM13006;s__HGM13006 sp905202605</t>
@@ -4702,19 +4702,19 @@
     <t>SRR30598618_clean_bin.85.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.85.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.85.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.86.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.86.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.86.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598618_clean_bin.88.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598618_clean_bin.88.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598618_clean_bin.88.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Rikenellaceae;g__Alistipes;s__Alistipes communis</t>
@@ -4726,7 +4726,7 @@
     <t>SRR30598620_clean_bin.10.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.10.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.10.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598620</t>
@@ -4735,7 +4735,7 @@
     <t>SRR30598620_clean_bin.104.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.104.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.104.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Chlamydiota;c__Chlamydiia;o__Chlamydiales;f__Chlamydiaceae;g__Chlamydia;s__</t>
@@ -4744,7 +4744,7 @@
     <t>SRR30598620_clean_bin.11.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.11.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.11.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__CAG-115;s__CAG-115 sp900768125</t>
@@ -4756,7 +4756,7 @@
     <t>SRR30598620_clean_bin.12.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.12.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.12.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Pseudomonadota;c__Gammaproteobacteria;o__Enterobacterales;f__Succinivibrionaceae;g__WG-1;s__WG-1 sp900539665</t>
@@ -4768,7 +4768,7 @@
     <t>SRR30598620_clean_bin.13.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.13.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.13.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__CAG-272;g__CAG-841;s__CAG-841 sp900544285</t>
@@ -4780,7 +4780,7 @@
     <t>SRR30598620_clean_bin.14.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.14.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.14.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Christensenellales;f__CAG-138;g__PeH17;s__PeH17 sp000435055</t>
@@ -4792,7 +4792,7 @@
     <t>SRR30598620_clean_bin.16.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.16.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.16.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Verrucomicrobiota;c__Verrucomicrobiia;o__Opitutales;f__Intestinicryptomonadaceae;g__Merdousia;s__Merdousia sp021641325</t>
@@ -4804,7 +4804,7 @@
     <t>SRR30598620_clean_bin.24.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.24.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.24.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__UMGS363;s__UMGS363 sp900768245</t>
@@ -4816,7 +4816,7 @@
     <t>SRR30598620_clean_bin.25.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.25.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.25.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Christensenellales;f__CAG-138;g__RUG472;s__RUG472 sp900545265</t>
@@ -4828,7 +4828,7 @@
     <t>SRR30598620_clean_bin.27.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.27.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.27.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Acutalibacteraceae;g__UBA1081;s__UBA1081 sp022763825</t>
@@ -4840,7 +4840,7 @@
     <t>SRR30598620_clean_bin.3.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.3.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.3.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Negativicutes;o__Acidaminococcales;f__Acidaminococcaceae;g__Phascolarctobacterium_A;s__Phascolarctobacterium_A sp934190775</t>
@@ -4852,7 +4852,7 @@
     <t>SRR30598620_clean_bin.31.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.31.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.31.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Christensenellales;f__Borkfalkiaceae;g__UBA4636;s__UBA4636 sp934273135</t>
@@ -4864,13 +4864,13 @@
     <t>SRR30598620_clean_bin.32.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.32.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.32.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598620_clean_bin.38.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.38.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.38.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__UBA932;g__Cryptobacteroides;s__Cryptobacteroides sp934725575</t>
@@ -4882,7 +4882,7 @@
     <t>SRR30598620_clean_bin.39.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.39.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.39.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__UBA2821;s__UBA2821 sp002351535</t>
@@ -4894,7 +4894,7 @@
     <t>SRR30598620_clean_bin.4.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.4.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.4.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Butyricicoccaceae;g__Butyricicoccus_A;s__Butyricicoccus_A intestinisimiae</t>
@@ -4906,19 +4906,19 @@
     <t>SRR30598620_clean_bin.40.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.40.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.40.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598620_clean_bin.48.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.48.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.48.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598620_clean_bin.59.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.59.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.59.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Oscillospiraceae;g__Limivicinus;s__Limivicinus sp934572335</t>
@@ -4930,13 +4930,13 @@
     <t>SRR30598620_clean_bin.66.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.66.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.66.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598620_clean_bin.69.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.69.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.69.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Bacteroidaceae;g__Prevotella;s__Prevotella sp900552675</t>
@@ -4948,13 +4948,13 @@
     <t>SRR30598620_clean_bin.71.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.71.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.71.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598620_clean_bin.72.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.72.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.72.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Christensenellales;f__CAG-138;g__SFEL01;s__SFEL01 sp004557245</t>
@@ -4966,7 +4966,7 @@
     <t>SRR30598620_clean_bin.73.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.73.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.73.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Bacteroidaceae;g__Bacteroides;s__Bacteroides caccae</t>
@@ -4978,13 +4978,13 @@
     <t>SRR30598620_clean_bin.74.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.74.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.74.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598620_clean_bin.75.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.75.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.75.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Acutalibacteraceae;g__Eubacterium_R;s__Eubacterium_R sp003526845</t>
@@ -4996,7 +4996,7 @@
     <t>SRR30598620_clean_bin.8.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.8.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.8.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__CAG-272;g__RGIG3994;s__RGIG3994 sp934378145</t>
@@ -5008,13 +5008,13 @@
     <t>SRR30598620_clean_bin.80.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.80.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.80.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598620_clean_bin.82.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.82.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.82.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Peptostreptococcales;f__Anaerovoracaceae;g__CAG-238;s__CAG-238 sp000435615</t>
@@ -5026,7 +5026,7 @@
     <t>SRR30598620_clean_bin.84.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.84.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.84.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__SFIE01;s__SFIE01 sp004555405</t>
@@ -5038,7 +5038,7 @@
     <t>SRR30598620_clean_bin.88.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.88.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.88.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Butyrivibrio_A;s__Butyrivibrio_A sp000431815</t>
@@ -5050,13 +5050,13 @@
     <t>SRR30598620_clean_bin.9.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598620_clean_bin.9.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598620_clean_bin.9.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598623_bin.10.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598623_bin.10.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598623_bin.10.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598623</t>
@@ -5065,7 +5065,7 @@
     <t>SRR30598623_bin.3.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598623_bin.3.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598623_bin.3.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Lactobacillales;f__Streptococcaceae;g__Streptococcus;s__Streptococcus sp959025735</t>
@@ -5077,13 +5077,13 @@
     <t>SRR30598623_bin.5.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598623_bin.5.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598623_bin.5.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598623_bin.6.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598623_bin.6.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598623_bin.6.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Negativicutes;o__Veillonellales;f__Veillonellaceae;g__Veillonella;s__Veillonella parvula_I</t>
@@ -5095,13 +5095,13 @@
     <t>SRR30598623_bin.7.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598623_bin.7.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598623_bin.7.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624_bin.1.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.1.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.1.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624</t>
@@ -5110,13 +5110,13 @@
     <t>SRR30598624_bin.10.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.10.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.10.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624_bin.14.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.14.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.14.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Mediterraneibacter;s__Mediterraneibacter faecis</t>
@@ -5128,19 +5128,19 @@
     <t>SRR30598624_bin.17.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.17.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.17.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624_bin.2.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.2.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.2.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624_bin.22.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.22.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.22.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Lactobacillales;f__Lactobacillaceae;g__Weissella;s__Weissella confusa</t>
@@ -5152,19 +5152,19 @@
     <t>SRR30598624_bin.24.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.24.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.24.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624_bin.25.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.25.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.25.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624_bin.27.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.27.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.27.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Lactobacillales;f__Enterococcaceae;g__Enterococcus;s__Enterococcus faecalis</t>
@@ -5176,19 +5176,19 @@
     <t>SRR30598624_bin.29.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.29.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.29.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624_bin.3.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.3.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.3.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598624_bin.7.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.7.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.7.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Tissierellales;f__Tissierellaceae;g__JAVKTS01;s__</t>
@@ -5197,7 +5197,7 @@
     <t>SRR30598624_bin.9.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598624_bin.9.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598624_bin.9.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__Faecalibacterium;s__Faecalibacterium prausnitzii_E</t>
@@ -5209,7 +5209,7 @@
     <t>SRR30598629_bin.1.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.1.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.1.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629</t>
@@ -5218,7 +5218,7 @@
     <t>SRR30598629_bin.11.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.11.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.11.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Anthropogastromicrobium;s__Anthropogastromicrobium aceti</t>
@@ -5230,7 +5230,7 @@
     <t>SRR30598629_bin.14.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.14.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.14.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Pseudomonadota;c__Alphaproteobacteria;o__Rs-D84;f__Rs-D84;g__Enterousia;s__Enterousia sp900550565</t>
@@ -5242,13 +5242,13 @@
     <t>SRR30598629_bin.15.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.15.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.15.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.17.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.17.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.17.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Oscillospiraceae;g__Apopatocola;s__Apopatocola sp003522945</t>
@@ -5260,7 +5260,7 @@
     <t>SRR30598629_bin.18.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.18.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.18.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Bacteroidaceae;g__Prevotella;s__Prevotella sp002299635</t>
@@ -5272,31 +5272,31 @@
     <t>SRR30598629_bin.2.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.2.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.2.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.20.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.20.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.20.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.24.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.24.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.24.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.28.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.28.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.28.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.33.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.33.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.33.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__Angelakisella;s__Angelakisella sp900547385</t>
@@ -5308,25 +5308,25 @@
     <t>SRR30598629_bin.36.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.36.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.36.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.38.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.38.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.38.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.40.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.40.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.40.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.41.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.41.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.41.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__CAG-272;g__UMGS1696;s__UMGS1696 sp900753285</t>
@@ -5338,19 +5338,19 @@
     <t>SRR30598629_bin.44.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.44.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.44.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.45.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.45.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.45.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.50.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.50.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.50.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Lactobacillales;f__Enterococcaceae;g__Enterococcus_B;s__Enterococcus_B lactis</t>
@@ -5362,19 +5362,19 @@
     <t>SRR30598629_bin.51.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.51.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.51.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.56.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.56.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.56.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.59.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.59.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.59.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Negativicutes;o__Selenomonadales;f__Selenomonadaceae;g__Mitsuokella;s__Mitsuokella multacida</t>
@@ -5386,7 +5386,7 @@
     <t>SRR30598629_bin.6.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.6.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.6.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Acutalibacteraceae;g__CAG-488;s__CAG-488 sp000434055</t>
@@ -5398,25 +5398,25 @@
     <t>SRR30598629_bin.60.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.60.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.60.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.61.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.61.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.61.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.63.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.63.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.63.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.66.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.66.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.66.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Actinomycetota;c__Coriobacteriia;o__Coriobacteriales;f__Atopobiaceae;g__Parolsenella;s__Parolsenella massiliensis</t>
@@ -5428,31 +5428,31 @@
     <t>SRR30598629_bin.7.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.7.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.7.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.72.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.72.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.72.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.73.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.73.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.73.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.74.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.74.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.74.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.75.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.75.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.75.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Oribacterium;s__Oribacterium sp937927445</t>
@@ -5464,13 +5464,13 @@
     <t>SRR30598629_bin.76.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.76.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.76.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.79.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.79.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.79.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Acutalibacteraceae;g__RGIG4076;s__RGIG4076 sp905198155</t>
@@ -5482,13 +5482,13 @@
     <t>SRR30598629_bin.82.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.82.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.82.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598629_bin.9.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598629_bin.9.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598629_bin.9.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__CAG-791;s__CAG-791 sp000431495</t>
@@ -5500,7 +5500,7 @@
     <t>SRR30598636_bin.1.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.1.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.1.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636</t>
@@ -5509,7 +5509,7 @@
     <t>SRR30598636_bin.10.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.10.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.10.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Agathobacter;s__Agathobacter sp900546625</t>
@@ -5521,13 +5521,13 @@
     <t>SRR30598636_bin.19.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.19.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.19.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.20.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.20.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.20.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Negativicutes;o__Selenomonadales;f__Selenomonadaceae;g__Anaerovibrio;s__Anaerovibrio sp900548165</t>
@@ -5539,25 +5539,25 @@
     <t>SRR30598636_bin.22.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.22.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.22.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.29.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.29.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.29.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.43.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.43.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.43.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.44.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.44.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.44.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Lactobacillales;f__Enterococcaceae;g__Enterococcus_G;s__Enterococcus_G sp913775425</t>
@@ -5569,7 +5569,7 @@
     <t>SRR30598636_bin.46.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.46.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.46.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Pseudomonadota;c__Alphaproteobacteria;o__RF32;f__CAG-239;g__RUG410;s__RUG410 sp934229625</t>
@@ -5581,25 +5581,25 @@
     <t>SRR30598636_bin.47.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.47.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.47.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.5.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.5.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.5.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.50.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.50.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.50.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.51.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.51.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.51.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Bacteroidaceae;g__Prevotella;s__Prevotella sp000436915</t>
@@ -5611,7 +5611,7 @@
     <t>SRR30598636_bin.52.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.52.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.52.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Lactobacillales;f__Streptococcaceae;g__Streptococcus;s__Streptococcus salivarius</t>
@@ -5623,13 +5623,13 @@
     <t>SRR30598636_bin.54.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.54.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.54.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.55.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.55.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.55.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Butyricicoccaceae;g__Agathobaculum;s__Agathobaculum sp934504345</t>
@@ -5641,19 +5641,19 @@
     <t>SRR30598636_bin.7.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.7.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.7.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598636_bin.8.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598636_bin.8.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598636_bin.8.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.10.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.10.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.10.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637</t>
@@ -5668,85 +5668,85 @@
     <t>SRR30598637_bin.13.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.13.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.13.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.14.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.14.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.14.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.15.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.15.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.15.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.18.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.18.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.18.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.2.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.2.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.2.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.20.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.20.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.20.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.28.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.28.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.28.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.31.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.31.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.31.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.32.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.32.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.32.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.34.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.34.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.34.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.35.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.35.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.35.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.4.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.4.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.4.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.41.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.41.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.41.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.42.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.42.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.42.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Marinifilaceae;g__Butyricimonas;s__Butyricimonas faecalis</t>
@@ -5758,7 +5758,7 @@
     <t>SRR30598637_bin.43.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.43.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.43.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Desulfobacterota_I;c__Desulfovibrionia;o__Desulfovibrionales;f__Desulfovibrionaceae;g__Desulfovibrio;s__Desulfovibrio fairfieldensis_A</t>
@@ -5770,25 +5770,25 @@
     <t>SRR30598637_bin.44.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.44.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.44.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.6.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.6.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.6.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.7.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.7.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.7.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598637_bin.8.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.8.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.8.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Rikenellaceae;g__Alistipes_A;s__Alistipes_A ihumii</t>
@@ -5800,13 +5800,13 @@
     <t>SRR30598637_bin.9.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598637_bin.9.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598637_bin.9.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.1.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.1.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.1.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639</t>
@@ -5821,7 +5821,7 @@
     <t>SRR30598639_clean_bin.14.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.14.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.14.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Roseburia_C;s__Roseburia_C amylophila</t>
@@ -5833,7 +5833,7 @@
     <t>SRR30598639_clean_bin.16.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.16.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.16.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__CAG-272;g__UMGS902;s__UMGS902 sp934467415</t>
@@ -5845,13 +5845,13 @@
     <t>SRR30598639_clean_bin.22.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.22.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.22.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.26.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.26.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.26.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Negativicutes;o__Acidaminococcales;f__Acidaminococcaceae;g__Phascolarctobacterium_A;s__Phascolarctobacterium_A sp022718015</t>
@@ -5863,13 +5863,13 @@
     <t>SRR30598639_clean_bin.30.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.30.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.30.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.32.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.32.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.32.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Oscillospiraceae;g__CAG-103;s__CAG-103 sp900543625</t>
@@ -5881,13 +5881,13 @@
     <t>SRR30598639_clean_bin.42.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.42.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.42.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.48.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.48.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.48.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Gallintestinimicrobium;s__Gallintestinimicrobium propionicum</t>
@@ -5899,13 +5899,13 @@
     <t>SRR30598639_clean_bin.5.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.5.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.5.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.50.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.50.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.50.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Bacteroidaceae;g__Alloprevotella;s__Alloprevotella sp900540885</t>
@@ -5917,19 +5917,19 @@
     <t>SRR30598639_clean_bin.52.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.52.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.52.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.53.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.53.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.53.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.55.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.55.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.55.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__CAG-115;s__CAG-115 sp003531585</t>
@@ -5941,19 +5941,19 @@
     <t>SRR30598639_clean_bin.56.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.56.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.56.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.6.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.6.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.6.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.61.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.61.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.61.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Roseburia;s__Roseburia sp902781225</t>
@@ -5965,25 +5965,25 @@
     <t>SRR30598639_clean_bin.63.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.63.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.63.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.66.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.66.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.66.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.67.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.67.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.67.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598639_clean_bin.8.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598639_clean_bin.8.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598639_clean_bin.8.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Wujia;s__Wujia hominis</t>
@@ -5995,7 +5995,7 @@
     <t>SRR30598644_bin.10.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.10.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.10.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644</t>
@@ -6004,31 +6004,31 @@
     <t>SRR30598644_bin.13.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.13.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.13.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.14.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.14.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.14.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.15.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.15.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.15.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.16.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.16.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.16.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.23.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.23.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.23.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Lactobacillales;f__Streptococcaceae;g__Streptococcus;s__Streptococcus hominis</t>
@@ -6040,37 +6040,37 @@
     <t>SRR30598644_bin.26.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.26.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.26.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.27.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.27.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.27.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.28.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.28.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.28.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.29.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.29.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.29.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.3.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.3.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.3.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.30.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.30.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.30.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Otoolea;s__Otoolea symbiosa</t>
@@ -6082,37 +6082,37 @@
     <t>SRR30598644_bin.31.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.31.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.31.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.33.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.33.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.33.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.35.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.35.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.35.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.38.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.38.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.38.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.39.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.39.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.39.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.40.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.40.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.40.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacteroidota;c__Bacteroidia;o__Bacteroidales;f__Bacteroidaceae;g__Prevotella;s__Prevotella sp022741625</t>
@@ -6124,7 +6124,7 @@
     <t>SRR30598644_bin.41.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.41.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.41.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Lactobacillales;f__Streptococcaceae;g__Streptococcus;s__Streptococcus infantarius</t>
@@ -6136,25 +6136,25 @@
     <t>SRR30598644_bin.42.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.42.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.42.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.43.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.43.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.43.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598644_bin.46.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598644_bin.46.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598644_bin.46.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.1.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.1.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.1.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645</t>
@@ -6163,13 +6163,13 @@
     <t>SRR30598645_clean_bin.15.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.15.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.15.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.2.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.2.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.2.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__Ruminiclostridium_E;s__Ruminiclostridium_E sp900539195</t>
@@ -6181,37 +6181,37 @@
     <t>SRR30598645_clean_bin.21.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.21.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.21.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.22.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.22.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.22.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.23.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.23.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.23.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.24.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.24.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.24.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.27.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.27.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.27.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.32.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.32.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.32.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Ruminococcaceae;g__Hominimerdicola;s__Hominimerdicola sp934435205</t>
@@ -6223,25 +6223,25 @@
     <t>SRR30598645_clean_bin.35.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.35.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.35.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.37.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.37.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.37.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.40.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.40.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.40.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.41.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.41.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.41.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Actinomycetota;c__Actinomycetes;o__Actinomycetales;f__Bifidobacteriaceae;g__Bifidobacterium;s__</t>
@@ -6250,31 +6250,31 @@
     <t>SRR30598645_clean_bin.43.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.43.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.43.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.49.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.49.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.49.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.5.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.5.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.5.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.52.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.52.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.52.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.54.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.54.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.54.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Agathobacter;s__Agathobacter sp900548765</t>
@@ -6286,7 +6286,7 @@
     <t>SRR30598645_clean_bin.56.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.56.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.56.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Negativicutes;o__Veillonellales;f__Dialisteraceae;g__Dialister;s__</t>
@@ -6295,19 +6295,19 @@
     <t>SRR30598645_clean_bin.59.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.59.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.59.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.60.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.60.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.60.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.64.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.64.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.64.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__Mediterraneibacter;s__Mediterraneibacter sp934309345</t>
@@ -6319,13 +6319,13 @@
     <t>SRR30598645_clean_bin.65.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.65.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.65.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.66.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.66.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.66.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Bacilli;o__Erysipelotrichales;f__Erysipelotrichaceae;g__Bulleidia;s__Bulleidia sp900539965</t>
@@ -6337,13 +6337,13 @@
     <t>SRR30598645_clean_bin.67.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.67.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.67.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.71.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.71.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.71.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Oscillospiraceae;g__F23-B02;s__F23-B02 sp002472405</t>
@@ -6355,7 +6355,7 @@
     <t>SRR30598645_clean_bin.72.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.72.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.72.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Lachnospirales;f__Lachnospiraceae;g__CAG-632;s__CAG-632 sp000431515</t>
@@ -6367,19 +6367,19 @@
     <t>SRR30598645_clean_bin.81.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.81.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.81.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.82.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.82.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.82.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598645_clean_bin.86.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.86.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.86.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Negativicutes;o__Acidaminococcales;f__Acidaminococcaceae;g__Phascolarctobacterium_A;s__Phascolarctobacterium_A sp902463975</t>
@@ -6391,13 +6391,13 @@
     <t>SRR30598645_clean_bin.87.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598645_clean_bin.87.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598645_clean_bin.87.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.1.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.1.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.1.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646</t>
@@ -6412,61 +6412,61 @@
     <t>SRR30598646_bin.10.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.10.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.10.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.12.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.12.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.12.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.13.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.13.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.13.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.14.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.14.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.14.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.17.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.17.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.17.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.18.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.18.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.18.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.22.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.22.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.22.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.23.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.23.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.23.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.24.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.24.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.24.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.26.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.26.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.26.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Oscillospiraceae;g__CAG-103;s__CAG-103 sp900317855</t>
@@ -6478,19 +6478,19 @@
     <t>SRR30598646_bin.28.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.28.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.28.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.33.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.33.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.33.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.34.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.34.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.34.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Acutalibacteraceae;g__CAG-964;s__CAG-964 sp000435335</t>
@@ -6502,73 +6502,73 @@
     <t>SRR30598646_bin.39.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.39.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.39.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.41.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.41.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.41.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.42.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.42.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.42.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.44.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.44.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.44.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.46.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.46.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.46.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.47.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.47.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.47.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.49.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.49.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.49.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.5.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.5.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.5.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.52.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.52.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.52.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.53.permissive</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.53.permissive_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.53.permissive_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.56.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.56.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.56.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.57.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.57.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.57.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Oscillospirales;f__Oscillospiraceae;g__Vescimonas;s__Vescimonas cirricatena</t>
@@ -6580,37 +6580,37 @@
     <t>SRR30598646_bin.58.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.58.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.58.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.61.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.61.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.61.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.67.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.67.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.67.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.69.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.69.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.69.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.7.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.7.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.7.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.70.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.70.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.70.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Pseudomonadota;c__Gammaproteobacteria;o__Burkholderiales;f__Burkholderiaceae;g__Sutterella;s__Sutterella sp949287305</t>
@@ -6622,13 +6622,13 @@
     <t>SRR30598646_bin.71.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.71.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.71.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598646_bin.9.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598646_bin.9.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598646_bin.9.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>d__Bacteria;p__Bacillota;c__Clostridia;o__Christensenellales;f__CAG-138;g__Phil1;s__Phil1 sp001940855</t>
@@ -6640,7 +6640,7 @@
     <t>SRR30598652_bin.14.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.14.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.14.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598652</t>
@@ -6649,55 +6649,55 @@
     <t>SRR30598652_bin.16.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.16.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.16.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598652_bin.18.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.18.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.18.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598652_bin.20.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.20.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.20.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598652_bin.23.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.23.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.23.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598652_bin.27.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.27.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.27.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598652_bin.34.strict</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.34.strict_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.34.strict_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598652_bin.4.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.4.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.4.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598652_bin.5.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598652_bin.5.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598652_bin.5.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598655_clean_bin.4.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598655_clean_bin.4.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598655_clean_bin.4.orig_filtered_kept_contigs.fa</t>
   </si>
   <si>
     <t>SRR30598655</t>
@@ -6706,7 +6706,7 @@
     <t>SRR30598655_clean_bin.7.orig</t>
   </si>
   <si>
-    <t>cleaned_SRR30598655_clean_bin.7.orig_filtered_kept_contigs</t>
+    <t>cleaned_SRR30598655_clean_bin.7.orig_filtered_kept_contigs.fa</t>
   </si>
 </sst>
 </file>
